--- a/sample_data/계정별원장.xlsx
+++ b/sample_data/계정별원장.xlsx
@@ -482,13 +482,13 @@
         <v>50000000</v>
       </c>
       <c r="D2" t="n">
-        <v>987813000</v>
+        <v>1037960600</v>
       </c>
       <c r="E2" t="n">
-        <v>4663920</v>
+        <v>19789920</v>
       </c>
       <c r="F2" t="n">
-        <v>1033149080</v>
+        <v>1068170680</v>
       </c>
     </row>
     <row r="3">
@@ -506,10 +506,10 @@
         <v>12000000</v>
       </c>
       <c r="D3" t="n">
-        <v>93744300</v>
+        <v>141496500</v>
       </c>
       <c r="E3" t="n">
-        <v>60305100</v>
+        <v>108057300</v>
       </c>
       <c r="F3" t="n">
         <v>45439200</v>
@@ -530,13 +530,13 @@
         <v>8000000</v>
       </c>
       <c r="D4" t="n">
-        <v>4767420</v>
+        <v>20433220</v>
       </c>
       <c r="E4" t="n">
-        <v>23580620</v>
+        <v>88737220</v>
       </c>
       <c r="F4" t="n">
-        <v>26813200</v>
+        <v>76304000</v>
       </c>
     </row>
     <row r="5">
@@ -557,10 +557,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>92584800</v>
+        <v>140337000</v>
       </c>
       <c r="F5" t="n">
-        <v>92584800</v>
+        <v>140337000</v>
       </c>
     </row>
     <row r="6">
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>23580620</v>
+        <v>88737220</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>23580620</v>
+        <v>88737220</v>
       </c>
     </row>
     <row r="7">
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>928290800</v>
+        <v>930824400</v>
       </c>
       <c r="F7" t="n">
-        <v>928290800</v>
+        <v>930824400</v>
       </c>
     </row>
     <row r="8">
@@ -626,13 +626,13 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>607000</v>
+        <v>634200</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>607000</v>
+        <v>634200</v>
       </c>
     </row>
     <row r="9">
@@ -653,10 +653,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1159500</v>
+        <v>1588300</v>
       </c>
       <c r="F9" t="n">
-        <v>1159500</v>
+        <v>1588300</v>
       </c>
     </row>
     <row r="10">
